--- a/entrée.xlsx
+++ b/entrée.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25427"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E782B2-A424-488C-AD4A-7AFCC8BC01F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FA133B-8108-4397-86E2-237A8649CD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5775" yWindow="4845" windowWidth="28800" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menu_1" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="341">
   <si>
     <t>semaine</t>
   </si>
@@ -934,9 +934,6 @@
   </si>
   <si>
     <t>22-08-2022</t>
-  </si>
-  <si>
-    <t>16-09-2020</t>
   </si>
   <si>
     <t>crème de poireaut</t>
@@ -1728,7 +1725,7 @@
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
@@ -1767,19 +1764,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>291</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>102</v>
@@ -1793,10 +1790,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>70</v>
@@ -1808,7 +1805,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>74</v>
@@ -1846,7 +1843,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>196</v>
@@ -1858,7 +1855,7 @@
         <v>233</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>246</v>
@@ -1896,13 +1893,13 @@
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>236</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>291</v>
@@ -1961,7 +1958,7 @@
         <v>114</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>113</v>
@@ -1994,7 +1991,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>72</v>
@@ -2012,7 +2009,7 @@
         <v>71</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -2023,7 +2020,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>88</v>
@@ -2032,7 +2029,7 @@
         <v>235</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>239</v>
@@ -2041,7 +2038,7 @@
         <v>104</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2079,7 +2076,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>179</v>
@@ -2088,7 +2085,7 @@
         <v>240</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>238</v>
@@ -2138,7 +2135,7 @@
         <v>170</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>199</v>
@@ -2153,7 +2150,7 @@
         <v>182</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2200,7 +2197,7 @@
         <v>114</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>113</v>
@@ -2563,10 +2560,10 @@
         <v>117</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>15</v>
@@ -2583,10 +2580,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>245</v>
@@ -2633,16 +2630,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>116</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>183</v>
@@ -2686,16 +2683,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>249</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>247</v>
@@ -2748,7 +2745,7 @@
         <v>75</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>141</v>
@@ -2787,16 +2784,16 @@
         <v>26</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>77</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>115</v>
@@ -2813,10 +2810,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>245</v>
@@ -2872,13 +2869,13 @@
         <v>28</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>242</v>
@@ -2925,16 +2922,16 @@
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>243</v>
@@ -2987,7 +2984,7 @@
         <v>75</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E20" s="21" t="s">
         <v>141</v>

--- a/entrée.xlsx
+++ b/entrée.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FA133B-8108-4397-86E2-237A8649CD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13291610-B603-47C6-86AD-693F2B5D834E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2625" yWindow="60" windowWidth="17340" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menu_1" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="342">
   <si>
     <t>semaine</t>
   </si>
@@ -933,9 +933,6 @@
     <t>***</t>
   </si>
   <si>
-    <t>22-08-2022</t>
-  </si>
-  <si>
     <t>crème de poireaut</t>
   </si>
   <si>
@@ -1054,6 +1051,12 @@
   </si>
   <si>
     <t xml:space="preserve">soupe aux lentilles et au curry </t>
+  </si>
+  <si>
+    <t>m/j/aaaa</t>
+  </si>
+  <si>
+    <t>9/5/2022</t>
   </si>
 </sst>
 </file>
@@ -1174,16 +1177,16 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Lucida Handwriting"/>
       <family val="4"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="22"/>
       <color indexed="8"/>
-      <name val="Lucida Handwriting"/>
-      <family val="4"/>
+      <name val="Lucida Bright"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1257,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1321,9 +1324,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1340,13 +1340,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1367,7 +1364,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1691,7 +1688,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
     <col min="2" max="8" width="35.7109375" customWidth="1"/>
@@ -1724,9 +1721,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="32" t="s">
-        <v>300</v>
-      </c>
+      <c r="A2" s="32"/>
       <c r="B2" s="17">
         <v>22</v>
       </c>
@@ -1750,7 +1745,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="31" t="s">
+        <v>340</v>
+      </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
@@ -1760,23 +1757,23 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="54" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>291</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>102</v>
@@ -1786,14 +1783,14 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="135" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>70</v>
@@ -1805,7 +1802,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>74</v>
@@ -1813,37 +1810,37 @@
     </row>
     <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
-      <c r="B6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="28" t="s">
+      <c r="B6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="81" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>196</v>
@@ -1855,7 +1852,7 @@
         <v>233</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>246</v>
@@ -1889,17 +1886,17 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>236</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>291</v>
@@ -1919,25 +1916,25 @@
     </row>
     <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A10" s="19"/>
-      <c r="B10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="28" t="s">
+      <c r="B10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1"/>
@@ -1945,7 +1942,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -1958,7 +1955,7 @@
         <v>114</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>113</v>
@@ -1979,19 +1976,19 @@
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="23"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>72</v>
@@ -2009,18 +2006,18 @@
         <v>71</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="135" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>88</v>
@@ -2029,7 +2026,7 @@
         <v>235</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>239</v>
@@ -2038,7 +2035,7 @@
         <v>104</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2046,25 +2043,25 @@
     </row>
     <row r="15" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A15" s="19"/>
-      <c r="B15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="B15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="1"/>
@@ -2072,11 +2069,11 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>179</v>
@@ -2085,7 +2082,7 @@
         <v>240</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>238</v>
@@ -2128,14 +2125,14 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="81" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>199</v>
@@ -2150,7 +2147,7 @@
         <v>182</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2158,25 +2155,25 @@
     </row>
     <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.35">
       <c r="A19" s="19"/>
-      <c r="B19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="28" t="s">
+      <c r="B19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="1"/>
@@ -2184,7 +2181,7 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="108" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -2197,7 +2194,7 @@
         <v>114</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>113</v>
@@ -2228,27 +2225,27 @@
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.35">
-      <c r="A25" s="31"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -2481,7 +2478,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
     <col min="2" max="8" width="35.7109375" customWidth="1"/>
@@ -2514,8 +2511,8 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="33" t="s">
-        <v>300</v>
+      <c r="A2" s="32" t="s">
+        <v>341</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
@@ -2540,7 +2537,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="31" t="s">
+        <v>340</v>
+      </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
@@ -2550,7 +2549,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="108" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -2560,10 +2559,10 @@
         <v>117</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>15</v>
@@ -2576,14 +2575,14 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="108" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>245</v>
@@ -2603,43 +2602,43 @@
     </row>
     <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
-      <c r="B6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="28" t="s">
+      <c r="B6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="108" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>116</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>183</v>
@@ -2679,20 +2678,20 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>249</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>247</v>
@@ -2709,25 +2708,25 @@
     </row>
     <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A10" s="19"/>
-      <c r="B10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="28" t="s">
+      <c r="B10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1"/>
@@ -2735,7 +2734,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="54" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -2745,7 +2744,7 @@
         <v>75</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>141</v>
@@ -2769,31 +2768,31 @@
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="23"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>77</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>115</v>
@@ -2806,14 +2805,14 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>245</v>
@@ -2836,25 +2835,25 @@
     </row>
     <row r="15" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A15" s="19"/>
-      <c r="B15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="B15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="1"/>
@@ -2862,20 +2861,20 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>242</v>
@@ -2917,21 +2916,21 @@
       <c r="K17" s="1"/>
       <c r="N17" s="14"/>
     </row>
-    <row r="18" spans="1:14" ht="135" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+    <row r="18" spans="1:14" ht="108" x14ac:dyDescent="0.35">
+      <c r="A18" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>243</v>
@@ -2948,25 +2947,25 @@
     </row>
     <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.35">
       <c r="A19" s="19"/>
-      <c r="B19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="28" t="s">
+      <c r="B19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="1"/>
@@ -2974,7 +2973,7 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="54" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -2984,7 +2983,7 @@
         <v>75</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E20" s="21" t="s">
         <v>141</v>
@@ -3018,27 +3017,27 @@
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.35">
-      <c r="A25" s="31"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -3271,7 +3270,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
     <col min="2" max="8" width="35.7109375" customWidth="1"/>
@@ -3304,8 +3303,8 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="33" t="s">
-        <v>300</v>
+      <c r="A2" s="32" t="s">
+        <v>341</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
@@ -3330,7 +3329,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="31" t="s">
+        <v>340</v>
+      </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
@@ -3340,7 +3341,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="81" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -3366,7 +3367,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="108" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -3393,30 +3394,30 @@
     </row>
     <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
-      <c r="B6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="28" t="s">
+      <c r="B6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="135" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
@@ -3469,7 +3470,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
@@ -3499,25 +3500,25 @@
     </row>
     <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A10" s="19"/>
-      <c r="B10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="28" t="s">
+      <c r="B10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1"/>
@@ -3525,7 +3526,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -3559,15 +3560,15 @@
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="23"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
@@ -3596,7 +3597,7 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -3626,25 +3627,25 @@
     </row>
     <row r="15" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A15" s="19"/>
-      <c r="B15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="B15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="1"/>
@@ -3652,7 +3653,7 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -3708,7 +3709,7 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="108" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -3738,25 +3739,25 @@
     </row>
     <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.35">
       <c r="A19" s="19"/>
-      <c r="B19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="28" t="s">
+      <c r="B19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="1"/>
@@ -3764,7 +3765,7 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="81" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -3808,27 +3809,27 @@
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.35">
-      <c r="A25" s="31"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -4061,7 +4062,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
     <col min="2" max="8" width="35.7109375" customWidth="1"/>
@@ -4094,8 +4095,8 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="33" t="s">
-        <v>300</v>
+      <c r="A2" s="32" t="s">
+        <v>341</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
@@ -4120,7 +4121,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="31" t="s">
+        <v>340</v>
+      </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
@@ -4130,7 +4133,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="54" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -4156,7 +4159,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="162" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -4183,30 +4186,30 @@
     </row>
     <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
-      <c r="B6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="28" t="s">
+      <c r="B6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="81" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
@@ -4259,7 +4262,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
@@ -4289,25 +4292,25 @@
     </row>
     <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A10" s="19"/>
-      <c r="B10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="28" t="s">
+      <c r="B10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1"/>
@@ -4315,7 +4318,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -4349,15 +4352,15 @@
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="23"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
@@ -4386,7 +4389,7 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="135" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -4416,25 +4419,25 @@
     </row>
     <row r="15" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A15" s="19"/>
-      <c r="B15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="B15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="1"/>
@@ -4442,7 +4445,7 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -4498,7 +4501,7 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="135" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -4528,25 +4531,25 @@
     </row>
     <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.35">
       <c r="A19" s="19"/>
-      <c r="B19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="28" t="s">
+      <c r="B19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="1"/>
@@ -4554,7 +4557,7 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="108" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -4598,27 +4601,27 @@
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.35">
-      <c r="A25" s="31"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -4851,7 +4854,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
     <col min="2" max="8" width="35.7109375" customWidth="1"/>
@@ -4884,8 +4887,8 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="33" t="s">
-        <v>300</v>
+      <c r="A2" s="32" t="s">
+        <v>341</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
@@ -4910,7 +4913,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="31" t="s">
+        <v>340</v>
+      </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
@@ -4920,7 +4925,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="81" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -4945,8 +4950,8 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="108" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+    <row r="5" spans="1:11" ht="81" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -4973,30 +4978,30 @@
     </row>
     <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
-      <c r="B6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="28" t="s">
+      <c r="B6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="81" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
@@ -5049,7 +5054,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
@@ -5079,25 +5084,25 @@
     </row>
     <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A10" s="19"/>
-      <c r="B10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="28" t="s">
+      <c r="B10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1"/>
@@ -5105,7 +5110,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="54" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -5139,15 +5144,15 @@
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="23"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
@@ -5175,8 +5180,8 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+    <row r="14" spans="1:11" ht="81" x14ac:dyDescent="0.35">
+      <c r="A14" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -5206,25 +5211,25 @@
     </row>
     <row r="15" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A15" s="19"/>
-      <c r="B15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="B15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="1"/>
@@ -5232,7 +5237,7 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -5286,7 +5291,7 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="108" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -5316,25 +5321,25 @@
     </row>
     <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.35">
       <c r="A19" s="19"/>
-      <c r="B19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="28" t="s">
+      <c r="B19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="1"/>
@@ -5342,7 +5347,7 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="54" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -5381,37 +5386,37 @@
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="H23" s="30"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="H23" s="29"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.35">
-      <c r="A25" s="31"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -5644,7 +5649,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
     <col min="2" max="8" width="35.7109375" customWidth="1"/>
@@ -5677,8 +5682,8 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="34" t="s">
-        <v>300</v>
+      <c r="A2" s="32" t="s">
+        <v>341</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
@@ -5703,7 +5708,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="31" t="s">
+        <v>340</v>
+      </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
@@ -5713,7 +5720,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="81" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -5739,7 +5746,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="108" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -5766,30 +5773,30 @@
     </row>
     <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
-      <c r="B6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="28" t="s">
+      <c r="B6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="108" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="21" t="s">
@@ -5842,7 +5849,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="21" t="s">
@@ -5872,25 +5879,25 @@
     </row>
     <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A10" s="19"/>
-      <c r="B10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="28" t="s">
+      <c r="B10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1"/>
@@ -5898,7 +5905,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -5932,15 +5939,15 @@
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="23"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
@@ -5969,7 +5976,7 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="108" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -5999,25 +6006,25 @@
     </row>
     <row r="15" spans="1:11" ht="27" x14ac:dyDescent="0.35">
       <c r="A15" s="19"/>
-      <c r="B15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="B15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="1"/>
@@ -6025,7 +6032,7 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="81" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -6081,7 +6088,7 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="81" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -6111,25 +6118,25 @@
     </row>
     <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.35">
       <c r="A19" s="19"/>
-      <c r="B19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="28" t="s">
+      <c r="B19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="1"/>
@@ -6137,7 +6144,7 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="81" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -6176,37 +6183,37 @@
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="H23" s="30"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="H23" s="29"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="27.75" x14ac:dyDescent="0.35">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.35">
-      <c r="A25" s="31"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>

--- a/entrée.xlsx
+++ b/entrée.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13291610-B603-47C6-86AD-693F2B5D834E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1975913F-AF0E-4CE1-9642-F12A541AA286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="60" windowWidth="17340" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14895" yWindow="2955" windowWidth="17340" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menu_1" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="342">
   <si>
     <t>semaine</t>
   </si>
@@ -1721,7 +1721,9 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="32"/>
+      <c r="A2" s="32" t="s">
+        <v>341</v>
+      </c>
       <c r="B2" s="17">
         <v>22</v>
       </c>

--- a/entrée.xlsx
+++ b/entrée.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1975913F-AF0E-4CE1-9642-F12A541AA286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE881051-971C-438F-A79D-73A133C90826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14895" yWindow="2955" windowWidth="17340" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menu_1" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="343">
   <si>
     <t>semaine</t>
   </si>
@@ -1057,6 +1057,9 @@
   </si>
   <si>
     <t>9/5/2022</t>
+  </si>
+  <si>
+    <t>9/12/2022</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1813,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
       <c r="B6" s="27" t="s">
         <v>9</v>
@@ -3306,7 +3309,7 @@
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="32" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B2" s="17">
         <v>22</v>
